--- a/output/graficos_dimensiones/comunal_i_ingr_a_2019_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2019_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:08</t>
+    <t xml:space="preserve">2026-09-09 23:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2019_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2019_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:01</t>
+    <t xml:space="preserve">2026-09-17 13:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2019_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2019_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:59</t>
+    <t xml:space="preserve">2026-09-23 12:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2019_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2019_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:28</t>
+    <t xml:space="preserve">2026-10-02 13:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2019_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2019_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:52</t>
+    <t xml:space="preserve">2026-10-05 10:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -653,7 +653,7 @@
         <v>2019</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>602100.62</v>
+        <v>602100.63</v>
       </c>
     </row>
     <row r="11">
